--- a/output/2022/sector_totals_2022.xlsx
+++ b/output/2022/sector_totals_2022.xlsx
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1735.277173509688</v>
+        <v>1735.277171139262</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>660.7178426546777</v>
+        <v>651.9218912677027</v>
       </c>
       <c r="E3" t="n">
-        <v>380.5486029700183</v>
+        <v>381.6120944574478</v>
       </c>
       <c r="F3" t="n">
-        <v>76.19207981083295</v>
+        <v>77.05981518128526</v>
       </c>
       <c r="G3" t="n">
-        <v>4.427990049950878</v>
+        <v>4.393621490338054</v>
       </c>
     </row>
     <row r="4">
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5989.300457805308</v>
+        <v>5989.300455434881</v>
       </c>
       <c r="C16" t="n">
         <v>545.1051435029821</v>
       </c>
       <c r="D16" t="n">
-        <v>4353.475573583101</v>
+        <v>4344.679622196126</v>
       </c>
       <c r="E16" t="n">
-        <v>6878.954155324403</v>
+        <v>6880.017646811832</v>
       </c>
       <c r="F16" t="n">
-        <v>1566.935918280072</v>
+        <v>1567.803653650524</v>
       </c>
       <c r="G16" t="n">
-        <v>34.42920758736232</v>
+        <v>34.3948390277495</v>
       </c>
     </row>
   </sheetData>

--- a/output/2022/sector_totals_2022.xlsx
+++ b/output/2022/sector_totals_2022.xlsx
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1735.277171139262</v>
+        <v>1838.377587283488</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>651.9218912677027</v>
+        <v>726.3762380426583</v>
       </c>
       <c r="E3" t="n">
-        <v>381.6120944574478</v>
+        <v>2026.858616712046</v>
       </c>
       <c r="F3" t="n">
-        <v>77.05981518128526</v>
+        <v>179.8335645730644</v>
       </c>
       <c r="G3" t="n">
-        <v>4.393621490338054</v>
+        <v>79.44988323157666</v>
       </c>
     </row>
     <row r="4">
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5989.300455434881</v>
+        <v>6092.400871579108</v>
       </c>
       <c r="C16" t="n">
         <v>545.1051435029821</v>
       </c>
       <c r="D16" t="n">
-        <v>4344.679622196126</v>
+        <v>4419.133968971082</v>
       </c>
       <c r="E16" t="n">
-        <v>6880.017646811832</v>
+        <v>8525.264169066431</v>
       </c>
       <c r="F16" t="n">
-        <v>1567.803653650524</v>
+        <v>1670.577403042304</v>
       </c>
       <c r="G16" t="n">
-        <v>34.3948390277495</v>
+        <v>109.4511007689881</v>
       </c>
     </row>
   </sheetData>

--- a/output/2022/sector_totals_2022.xlsx
+++ b/output/2022/sector_totals_2022.xlsx
@@ -492,13 +492,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1838.377587283488</v>
+        <v>1732.523738345539</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>105.8538489379484</v>
       </c>
       <c r="D3" t="n">
-        <v>726.3762380426583</v>
+        <v>726.3762380426582</v>
       </c>
       <c r="E3" t="n">
         <v>2026.858616712046</v>
@@ -507,7 +507,7 @@
         <v>179.8335645730644</v>
       </c>
       <c r="G3" t="n">
-        <v>79.44988323157666</v>
+        <v>79.44988323157665</v>
       </c>
     </row>
     <row r="4">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6092.400871579108</v>
+        <v>5986.547022641158</v>
       </c>
       <c r="C16" t="n">
-        <v>545.1051435029821</v>
+        <v>650.9589924409305</v>
       </c>
       <c r="D16" t="n">
         <v>4419.133968971082</v>
@@ -829,7 +829,7 @@
         <v>8525.264169066431</v>
       </c>
       <c r="F16" t="n">
-        <v>1670.577403042304</v>
+        <v>1670.577403042303</v>
       </c>
       <c r="G16" t="n">
         <v>109.4511007689881</v>

--- a/output/2022/sector_totals_2022.xlsx
+++ b/output/2022/sector_totals_2022.xlsx
@@ -470,7 +470,7 @@
         <v>2496.5</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>314.714</v>
       </c>
       <c r="D2" t="n">
         <v>1286.42</v>
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1732.523738345539</v>
+        <v>1849.487654264609</v>
       </c>
       <c r="C3" t="n">
-        <v>105.8538489379484</v>
+        <v>116.9637516095138</v>
       </c>
       <c r="D3" t="n">
-        <v>726.3762380426582</v>
+        <v>734.845608751519</v>
       </c>
       <c r="E3" t="n">
-        <v>2026.858616712046</v>
+        <v>2199.549970415716</v>
       </c>
       <c r="F3" t="n">
-        <v>179.8335645730644</v>
+        <v>190.8258766850863</v>
       </c>
       <c r="G3" t="n">
-        <v>79.44988323157665</v>
+        <v>87.33052067487218</v>
       </c>
     </row>
     <row r="4">
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5986.547022641158</v>
+        <v>6103.510938560228</v>
       </c>
       <c r="C16" t="n">
-        <v>650.9589924409305</v>
+        <v>976.7828951124959</v>
       </c>
       <c r="D16" t="n">
-        <v>4419.133968971082</v>
+        <v>4427.603339679942</v>
       </c>
       <c r="E16" t="n">
-        <v>8525.264169066431</v>
+        <v>8697.955522770102</v>
       </c>
       <c r="F16" t="n">
-        <v>1670.577403042303</v>
+        <v>1681.569715154325</v>
       </c>
       <c r="G16" t="n">
-        <v>109.4511007689881</v>
+        <v>117.3317382122836</v>
       </c>
     </row>
   </sheetData>
